--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.18023</v>
+        <v>16.99901</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68721</v>
+        <v>16.7277</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83989</v>
+        <v>16.98614</v>
       </c>
       <c r="F2" t="n">
-        <v>44.06702</v>
+        <v>43.14794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05054</v>
+        <v>0.05049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84504</v>
+        <v>1.87941</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67627</v>
+        <v>16.8074</v>
       </c>
       <c r="D3" t="n">
-        <v>16.38912</v>
+        <v>16.75192</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89408</v>
+        <v>16.78592</v>
       </c>
       <c r="F3" t="n">
-        <v>43.21521</v>
+        <v>42.45363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05156</v>
+        <v>0.05225</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83406</v>
+        <v>1.79671</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.91734</v>
+        <v>16.87024</v>
       </c>
       <c r="D4" t="n">
-        <v>16.63042</v>
+        <v>16.2573</v>
       </c>
       <c r="E4" t="n">
-        <v>17.06787</v>
+        <v>16.869</v>
       </c>
       <c r="F4" t="n">
-        <v>43.17188</v>
+        <v>42.55591</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05102</v>
+        <v>0.05046</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83285</v>
+        <v>1.86167</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.18853</v>
+        <v>17.05544</v>
       </c>
       <c r="D5" t="n">
-        <v>16.68524</v>
+        <v>16.85845</v>
       </c>
       <c r="E5" t="n">
-        <v>16.67801</v>
+        <v>17.00355</v>
       </c>
       <c r="F5" t="n">
-        <v>43.21235</v>
+        <v>43.16036</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04972</v>
+        <v>0.05057</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84382</v>
+        <v>1.85291</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.08592</v>
+        <v>16.84631</v>
       </c>
       <c r="D6" t="n">
-        <v>16.44247</v>
+        <v>16.65612</v>
       </c>
       <c r="E6" t="n">
-        <v>16.67184</v>
+        <v>16.77215</v>
       </c>
       <c r="F6" t="n">
-        <v>42.13378</v>
+        <v>43.37638</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05051</v>
+        <v>0.05085</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81716</v>
+        <v>1.79445</v>
       </c>
     </row>
     <row r="7">
@@ -585,461 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.65152</v>
+        <v>16.96885</v>
       </c>
       <c r="D7" t="n">
-        <v>16.94655</v>
+        <v>16.49437</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45046</v>
+        <v>16.67687</v>
       </c>
       <c r="F7" t="n">
-        <v>43.33197</v>
+        <v>43.31257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0509</v>
+        <v>0.05044</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84408</v>
+        <v>1.85173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83234</v>
+        <v>16.91344</v>
       </c>
       <c r="D8" t="n">
-        <v>16.84942</v>
+        <v>16.53714</v>
       </c>
       <c r="E8" t="n">
-        <v>16.80532</v>
+        <v>16.80521</v>
       </c>
       <c r="F8" t="n">
-        <v>42.87618</v>
+        <v>41.94625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05107</v>
+        <v>0.0513</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83884</v>
+        <v>1.82648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.4189</v>
+        <v>16.84351</v>
       </c>
       <c r="D9" t="n">
-        <v>16.85783</v>
+        <v>16.40202</v>
       </c>
       <c r="E9" t="n">
-        <v>16.76765</v>
+        <v>16.78832</v>
       </c>
       <c r="F9" t="n">
-        <v>42.79181</v>
+        <v>42.73102</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0505</v>
+        <v>0.05093</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84415</v>
+        <v>1.8572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.89046</v>
+        <v>17.00598</v>
       </c>
       <c r="D10" t="n">
-        <v>16.48421</v>
+        <v>16.65733</v>
       </c>
       <c r="E10" t="n">
-        <v>16.41081</v>
+        <v>16.78748</v>
       </c>
       <c r="F10" t="n">
-        <v>43.02139</v>
+        <v>43.03496</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05041</v>
+        <v>0.05084</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85623</v>
+        <v>1.83815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.57584</v>
+        <v>16.97192</v>
       </c>
       <c r="D11" t="n">
-        <v>16.58205</v>
+        <v>16.52102</v>
       </c>
       <c r="E11" t="n">
-        <v>16.89198</v>
+        <v>16.66034</v>
       </c>
       <c r="F11" t="n">
-        <v>43.3606</v>
+        <v>42.52372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05038</v>
+        <v>0.0512</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82895</v>
+        <v>1.83514</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.02413</v>
+        <v>16.98655</v>
       </c>
       <c r="D12" t="n">
-        <v>16.71163</v>
+        <v>16.686</v>
       </c>
       <c r="E12" t="n">
-        <v>16.74087</v>
+        <v>16.74278</v>
       </c>
       <c r="F12" t="n">
-        <v>42.816</v>
+        <v>41.81617</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05081</v>
+        <v>0.0507</v>
       </c>
       <c r="H12" t="n">
-        <v>1.80274</v>
+        <v>1.85709</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.96867</v>
+        <v>16.8191</v>
       </c>
       <c r="D13" t="n">
-        <v>16.95602</v>
+        <v>16.41999</v>
       </c>
       <c r="E13" t="n">
-        <v>16.93194</v>
+        <v>16.81265</v>
       </c>
       <c r="F13" t="n">
-        <v>41.87229</v>
+        <v>43.26328</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0516</v>
+        <v>0.05059</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82184</v>
+        <v>1.82569</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.92216</v>
+        <v>16.97444</v>
       </c>
       <c r="D14" t="n">
-        <v>16.81098</v>
+        <v>16.49031</v>
       </c>
       <c r="E14" t="n">
-        <v>16.40135</v>
+        <v>16.93931</v>
       </c>
       <c r="F14" t="n">
-        <v>43.64236</v>
+        <v>42.63794</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05147</v>
+        <v>0.05138</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83628</v>
+        <v>1.82297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.95776</v>
+        <v>17.20214</v>
       </c>
       <c r="D15" t="n">
-        <v>16.70064</v>
+        <v>16.62951</v>
       </c>
       <c r="E15" t="n">
-        <v>17.14011</v>
+        <v>16.77238</v>
       </c>
       <c r="F15" t="n">
-        <v>42.53142</v>
+        <v>43.3659</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04982</v>
+        <v>0.05152</v>
       </c>
       <c r="H15" t="n">
-        <v>1.87449</v>
+        <v>1.87145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.27623</v>
+        <v>17.20216</v>
       </c>
       <c r="D16" t="n">
-        <v>16.45763</v>
+        <v>16.34997</v>
       </c>
       <c r="E16" t="n">
-        <v>16.56038</v>
+        <v>16.84422</v>
       </c>
       <c r="F16" t="n">
-        <v>43.45593</v>
+        <v>42.70813</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05215</v>
+        <v>0.05169</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78975</v>
+        <v>1.82442</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.90818</v>
+        <v>17.14103</v>
       </c>
       <c r="D17" t="n">
-        <v>17.39119</v>
+        <v>16.50687</v>
       </c>
       <c r="E17" t="n">
-        <v>16.53728</v>
+        <v>16.94626</v>
       </c>
       <c r="F17" t="n">
-        <v>43.15013</v>
+        <v>42.80528</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05128</v>
+        <v>0.05158</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8691</v>
+        <v>1.82337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.0249</v>
+        <v>17.22357</v>
       </c>
       <c r="D18" t="n">
-        <v>16.67849</v>
+        <v>16.80208</v>
       </c>
       <c r="E18" t="n">
-        <v>17.07846</v>
+        <v>16.80607</v>
       </c>
       <c r="F18" t="n">
-        <v>42.80444</v>
+        <v>41.60757</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05085</v>
+        <v>0.0517</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86824</v>
+        <v>1.83594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.97581</v>
+        <v>16.9563</v>
       </c>
       <c r="D19" t="n">
-        <v>16.80132</v>
+        <v>16.75521</v>
       </c>
       <c r="E19" t="n">
-        <v>16.68889</v>
+        <v>16.82723</v>
       </c>
       <c r="F19" t="n">
-        <v>42.87082</v>
+        <v>42.77495</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0508</v>
+        <v>0.05146</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82645</v>
+        <v>1.79145</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.10553</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.68156</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.84543</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.65713</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05012</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.8241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.61066</v>
+        <v>17.33607</v>
       </c>
       <c r="D21" t="n">
-        <v>1.10909</v>
+        <v>16.438</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.06336</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43.54031</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.85156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6220599999999999</v>
+        <v>17.27402</v>
       </c>
       <c r="D22" t="n">
-        <v>1.13056</v>
+        <v>16.6429</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.74079</v>
+      </c>
+      <c r="F22" t="n">
+        <v>41.9664</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.80953</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.60747</v>
+        <v>17.08901</v>
       </c>
       <c r="D23" t="n">
-        <v>1.12885</v>
+        <v>16.54889</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.61443</v>
+      </c>
+      <c r="F23" t="n">
+        <v>41.71479</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.83669</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6173999999999999</v>
+        <v>16.79512</v>
       </c>
       <c r="D24" t="n">
-        <v>1.13797</v>
+        <v>16.55736</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.56207</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.53023</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.85032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.59861</v>
+        <v>17.17923</v>
       </c>
       <c r="D25" t="n">
-        <v>1.10704</v>
+        <v>16.70598</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.85465</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.07681</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.85673</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.61478</v>
+        <v>16.7231</v>
       </c>
       <c r="D26" t="n">
-        <v>1.11649</v>
+        <v>16.4426</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.58486</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.70986</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.85069</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.60502</v>
+        <v>17.18441</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11672</v>
+        <v>16.95393</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.08802</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42.69253</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.81889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6093</v>
+        <v>17.24248</v>
       </c>
       <c r="D28" t="n">
-        <v>1.10786</v>
+        <v>16.61953</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.02329</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.10787</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.83171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16.84041</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.35945</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.5967</v>
+      </c>
+      <c r="F29" t="n">
+        <v>43.01705</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.79949</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.77883</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.42716</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.73827</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.28077</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.85182</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.25817</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.87608</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.96236</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.39759</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.81113</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.07502</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.41441</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.72125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42.97911</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.82469</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.9734</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.64511</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.79112</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.56246</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05096</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.80963</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.93492</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.58196</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.88214</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42.3864</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.84675</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.85177</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.52602</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.65917</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.19573</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05036</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.84051</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.9321</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.32346</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.88134</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.14624</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.83025</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.0272</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.61784</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.69799</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42.58941</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.82905</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.21628</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.16743</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.69469</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.80602</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.81012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.68502</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.13666</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.55343</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.97343</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.33654</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.61746</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.10348</v>
+      <c r="C41" t="n">
+        <v>16.95231</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.10281</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.36709</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.94181</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.16129</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.72752</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.97086</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.51255</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.54781</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.39612</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.90463</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.08953</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.68009</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.99373</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.4559</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.6417</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.39582</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.48195</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.70517</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.38608</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.72069</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.93569</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.59537</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.73026</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.49238</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.10356</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.32539</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.51004</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.88313</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.65942</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.8451</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.22995</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.75564</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.41917</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.45791</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.70288</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.2868</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.35383</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.56458</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.16372</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.96361</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.91741</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.59926</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.48976</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.73856</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.77084</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.99708</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.76558</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.99737</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.57518</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.43495</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.00407</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.05016</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.72397</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.95976</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.66268</v>
+      </c>
+      <c r="D52" t="n">
+        <v>15.96538</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.6008</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.95829</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.28435</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.86114</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.36197</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.38664</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22.09789</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.10102</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.65374</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.1971</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.51165</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.18806</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.41157</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.75986</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15.97465</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.61352</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.12401</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.05298</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.05251</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.10016</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.56395</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22.05987</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.61824</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.81228</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.46187</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.63278</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22.01737</v>
+      </c>
+      <c r="G57" t="n">
+        <v>34.56881</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.63769</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15.96841</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.55638</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.84441</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.16398</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.56642</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.18074</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.21942</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.9705</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.55165</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.73008</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.95515</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.4432</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22.12911</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.47971</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.73363</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.15927</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.71819</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.25838</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.47439</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.43497</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16.08669</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.2033</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.25588</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.60372</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.91121</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.03474</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.62285</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.70789</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.4292</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17.2158</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15.94626</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.69789</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22.02085</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.02251</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16.96098</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.143</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.64034</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.4045</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.89104</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.58204</v>
+      </c>
+      <c r="D66" t="n">
+        <v>15.94773</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.53795</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.00535</v>
+      </c>
+      <c r="G66" t="n">
+        <v>33.98625</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>17.039</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.24685</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.68184</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.75368</v>
+      </c>
+      <c r="G67" t="n">
+        <v>34.32761</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.64527</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.08677</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.47036</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.24438</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.52195</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.51578</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15.8209</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.3517</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.95188</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.66301</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.82167</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15.80811</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.42529</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.68824</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.19489</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>17.05475</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16.21316</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.51003</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22.20354</v>
+      </c>
+      <c r="G71" t="n">
+        <v>35.11098</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.85611</v>
+      </c>
+      <c r="D72" t="n">
+        <v>15.92727</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.42367</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22.45161</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.50628</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.75453</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16.17653</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.48716</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.65152</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.57398</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.88867</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.07805</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.68551</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.85994</v>
+      </c>
+      <c r="G74" t="n">
+        <v>33.90068</v>
       </c>
     </row>
   </sheetData>
